--- a/backend/data/financials_by_company/0039.HK.xlsx
+++ b/backend/data/financials_by_company/0039.HK.xlsx
@@ -667,578 +667,578 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-344865.72381</v>
+        <v>881000</v>
       </c>
       <c r="C2" t="n">
-        <v>0.090683</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>17037000</v>
+        <v>90254000</v>
       </c>
       <c r="E2" t="n">
-        <v>-3803000</v>
+        <v>3524000</v>
       </c>
       <c r="F2" t="n">
-        <v>-3803000</v>
+        <v>3524000</v>
       </c>
       <c r="G2" t="n">
-        <v>-24163000</v>
+        <v>-170916000</v>
       </c>
       <c r="H2" t="n">
-        <v>36819000</v>
+        <v>162069000</v>
       </c>
       <c r="I2" t="n">
-        <v>139426000</v>
+        <v>767708000</v>
       </c>
       <c r="J2" t="n">
-        <v>13234000</v>
+        <v>93778000</v>
       </c>
       <c r="K2" t="n">
-        <v>-23585000</v>
+        <v>-68291000</v>
       </c>
       <c r="L2" t="n">
-        <v>-6650000</v>
+        <v>-99552000</v>
       </c>
       <c r="M2" t="n">
-        <v>7314000</v>
+        <v>101839000</v>
       </c>
       <c r="N2" t="n">
-        <v>664000</v>
+        <v>2287000</v>
       </c>
       <c r="O2" t="n">
-        <v>-20704865.72381</v>
+        <v>-173559000</v>
       </c>
       <c r="P2" t="n">
-        <v>-295808000</v>
+        <v>-170916000</v>
       </c>
       <c r="Q2" t="n">
-        <v>190595000</v>
+        <v>993217000</v>
       </c>
       <c r="R2" t="n">
-        <v>-11482000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>46275000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6225126000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6225126000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.0275</v>
+      </c>
       <c r="W2" t="n">
-        <v>-295808000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>-170916000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" t="n">
-        <v>-295808000</v>
+        <v>-170916000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-295808000</v>
+        <v>-170916000</v>
       </c>
       <c r="AB2" t="n">
-        <v>3934000</v>
+        <v>6374000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-299742000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-271645000</v>
-      </c>
+        <v>-177290000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>-28097000</v>
+        <v>-177290000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2802000</v>
+        <v>7160000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-30899000</v>
+        <v>-170130000</v>
       </c>
       <c r="AH2" t="n">
-        <v>44000</v>
+        <v>1427000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3803000</v>
+        <v>3524000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3803000</v>
+        <v>-3524000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-6650000</v>
+        <v>-99552000</v>
       </c>
       <c r="AL2" t="n">
-        <v>7314000</v>
+        <v>101839000</v>
       </c>
       <c r="AM2" t="n">
-        <v>664000</v>
+        <v>2287000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-8510000</v>
+        <v>-64432000</v>
       </c>
       <c r="AO2" t="n">
-        <v>51169000</v>
+        <v>225509000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1873000</v>
+        <v>93603000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>49313000</v>
+        <v>132186000</v>
       </c>
       <c r="AR2" t="n">
-        <v>7760000</v>
+        <v>23719000</v>
       </c>
       <c r="AS2" t="n">
-        <v>41553000</v>
+        <v>108467000</v>
       </c>
       <c r="AT2" t="n">
-        <v>42659000</v>
+        <v>161077000</v>
       </c>
       <c r="AU2" t="n">
-        <v>139426000</v>
+        <v>767708000</v>
       </c>
       <c r="AV2" t="n">
-        <v>182085000</v>
+        <v>928785000</v>
       </c>
       <c r="AW2" t="n">
-        <v>182085000</v>
+        <v>928785000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>5233.596854</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.008347</v>
       </c>
       <c r="D3" t="n">
-        <v>39118000</v>
+        <v>88521000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>627000</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>627000</v>
       </c>
       <c r="G3" t="n">
-        <v>-30847000</v>
+        <v>-218450000</v>
       </c>
       <c r="H3" t="n">
-        <v>45277000</v>
+        <v>164923000</v>
       </c>
       <c r="I3" t="n">
-        <v>159686000</v>
+        <v>795067000</v>
       </c>
       <c r="J3" t="n">
-        <v>39118000</v>
+        <v>89148000</v>
       </c>
       <c r="K3" t="n">
-        <v>-6159000</v>
+        <v>-75775000</v>
       </c>
       <c r="L3" t="n">
-        <v>-15368000</v>
+        <v>-146375000</v>
       </c>
       <c r="M3" t="n">
-        <v>15956000</v>
+        <v>148496000</v>
       </c>
       <c r="N3" t="n">
-        <v>588000</v>
+        <v>2121000</v>
       </c>
       <c r="O3" t="n">
-        <v>-30847000</v>
+        <v>-219071766.403146</v>
       </c>
       <c r="P3" t="n">
-        <v>-153317000</v>
+        <v>-218450000</v>
       </c>
       <c r="Q3" t="n">
-        <v>210143000</v>
+        <v>988908000</v>
       </c>
       <c r="R3" t="n">
-        <v>11456000</v>
+        <v>22786000</v>
       </c>
       <c r="S3" t="n">
-        <v>6327838000</v>
+        <v>6258701000</v>
       </c>
       <c r="T3" t="n">
-        <v>6327838000</v>
+        <v>6258701000</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0276</v>
+        <v>-0.0349</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0276</v>
+        <v>-0.0349</v>
       </c>
       <c r="W3" t="n">
-        <v>-153317000</v>
+        <v>-218450000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-153317000</v>
+        <v>-218450000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-153317000</v>
+        <v>-218450000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-7729000</v>
+        <v>3949000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-145588000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-122470000</v>
-      </c>
+        <v>-222399000</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-23118000</v>
+        <v>-222399000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1003000</v>
+        <v>-1872000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-22115000</v>
+        <v>-224271000</v>
       </c>
       <c r="AH3" t="n">
-        <v>921000</v>
+        <v>2368000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>627000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-627000</v>
+      </c>
       <c r="AK3" t="n">
-        <v>-15368000</v>
+        <v>-146375000</v>
       </c>
       <c r="AL3" t="n">
-        <v>15956000</v>
+        <v>148496000</v>
       </c>
       <c r="AM3" t="n">
-        <v>588000</v>
+        <v>2121000</v>
       </c>
       <c r="AN3" t="n">
-        <v>9586000</v>
+        <v>-58632000</v>
       </c>
       <c r="AO3" t="n">
-        <v>50457000</v>
+        <v>193841000</v>
       </c>
       <c r="AP3" t="n">
-        <v>22000</v>
+        <v>79254000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>50488000</v>
+        <v>115120000</v>
       </c>
       <c r="AR3" t="n">
-        <v>8033000</v>
+        <v>22924000</v>
       </c>
       <c r="AS3" t="n">
-        <v>42455000</v>
+        <v>92196000</v>
       </c>
       <c r="AT3" t="n">
-        <v>60043000</v>
+        <v>135209000</v>
       </c>
       <c r="AU3" t="n">
-        <v>159686000</v>
+        <v>795067000</v>
       </c>
       <c r="AV3" t="n">
-        <v>219729000</v>
+        <v>930276000</v>
       </c>
       <c r="AW3" t="n">
-        <v>219729000</v>
+        <v>930276000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>5233.596854</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008347</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>88521000</v>
+        <v>39118000</v>
       </c>
       <c r="E4" t="n">
-        <v>627000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>627000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-218450000</v>
+        <v>-30847000</v>
       </c>
       <c r="H4" t="n">
-        <v>164923000</v>
+        <v>45277000</v>
       </c>
       <c r="I4" t="n">
-        <v>795067000</v>
+        <v>159686000</v>
       </c>
       <c r="J4" t="n">
-        <v>89148000</v>
+        <v>39118000</v>
       </c>
       <c r="K4" t="n">
-        <v>-75775000</v>
+        <v>-6159000</v>
       </c>
       <c r="L4" t="n">
-        <v>-146375000</v>
+        <v>-15368000</v>
       </c>
       <c r="M4" t="n">
-        <v>148496000</v>
+        <v>15956000</v>
       </c>
       <c r="N4" t="n">
-        <v>2121000</v>
+        <v>588000</v>
       </c>
       <c r="O4" t="n">
-        <v>-219071766.403146</v>
+        <v>-30847000</v>
       </c>
       <c r="P4" t="n">
-        <v>-218450000</v>
+        <v>-153317000</v>
       </c>
       <c r="Q4" t="n">
-        <v>988908000</v>
+        <v>210143000</v>
       </c>
       <c r="R4" t="n">
-        <v>22786000</v>
+        <v>11456000</v>
       </c>
       <c r="S4" t="n">
-        <v>6258701000</v>
+        <v>6327838000</v>
       </c>
       <c r="T4" t="n">
-        <v>6258701000</v>
+        <v>6327838000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0349</v>
+        <v>-0.0276</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0349</v>
+        <v>-0.0276</v>
       </c>
       <c r="W4" t="n">
-        <v>-218450000</v>
+        <v>-153317000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-218450000</v>
+        <v>-153317000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-218450000</v>
+        <v>-153317000</v>
       </c>
       <c r="AB4" t="n">
-        <v>3949000</v>
+        <v>-7729000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-222399000</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>-145588000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-122470000</v>
+      </c>
       <c r="AE4" t="n">
-        <v>-222399000</v>
+        <v>-23118000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1872000</v>
+        <v>1003000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-224271000</v>
+        <v>-22115000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2368000</v>
+        <v>921000</v>
       </c>
       <c r="AI4" t="n">
-        <v>627000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-627000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>-146375000</v>
+        <v>-15368000</v>
       </c>
       <c r="AL4" t="n">
-        <v>148496000</v>
+        <v>15956000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2121000</v>
+        <v>588000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-58632000</v>
+        <v>9586000</v>
       </c>
       <c r="AO4" t="n">
-        <v>193841000</v>
+        <v>50457000</v>
       </c>
       <c r="AP4" t="n">
-        <v>79254000</v>
+        <v>22000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>115120000</v>
+        <v>50488000</v>
       </c>
       <c r="AR4" t="n">
-        <v>22924000</v>
+        <v>8033000</v>
       </c>
       <c r="AS4" t="n">
-        <v>92196000</v>
+        <v>42455000</v>
       </c>
       <c r="AT4" t="n">
-        <v>135209000</v>
+        <v>60043000</v>
       </c>
       <c r="AU4" t="n">
-        <v>795067000</v>
+        <v>159686000</v>
       </c>
       <c r="AV4" t="n">
-        <v>930276000</v>
+        <v>219729000</v>
       </c>
       <c r="AW4" t="n">
-        <v>930276000</v>
+        <v>219729000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>881000</v>
+        <v>-344865.72381</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.090683</v>
       </c>
       <c r="D5" t="n">
-        <v>90254000</v>
+        <v>17037000</v>
       </c>
       <c r="E5" t="n">
-        <v>3524000</v>
+        <v>-3803000</v>
       </c>
       <c r="F5" t="n">
-        <v>3524000</v>
+        <v>-3803000</v>
       </c>
       <c r="G5" t="n">
-        <v>-170916000</v>
+        <v>-24163000</v>
       </c>
       <c r="H5" t="n">
-        <v>162069000</v>
+        <v>36819000</v>
       </c>
       <c r="I5" t="n">
-        <v>767708000</v>
+        <v>139426000</v>
       </c>
       <c r="J5" t="n">
-        <v>93778000</v>
+        <v>13234000</v>
       </c>
       <c r="K5" t="n">
-        <v>-68291000</v>
+        <v>-23585000</v>
       </c>
       <c r="L5" t="n">
-        <v>-99552000</v>
+        <v>-6650000</v>
       </c>
       <c r="M5" t="n">
-        <v>101839000</v>
+        <v>7314000</v>
       </c>
       <c r="N5" t="n">
-        <v>2287000</v>
+        <v>664000</v>
       </c>
       <c r="O5" t="n">
-        <v>-173559000</v>
+        <v>-20704865.72381</v>
       </c>
       <c r="P5" t="n">
-        <v>-170916000</v>
+        <v>-295808000</v>
       </c>
       <c r="Q5" t="n">
-        <v>993217000</v>
+        <v>190595000</v>
       </c>
       <c r="R5" t="n">
-        <v>46275000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6225126000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>6225126000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.0275</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.0275</v>
-      </c>
+        <v>-11482000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-170916000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
+        <v>-295808000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>-170916000</v>
+        <v>-295808000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-170916000</v>
+        <v>-295808000</v>
       </c>
       <c r="AB5" t="n">
-        <v>6374000</v>
+        <v>3934000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-177290000</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>-299742000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-271645000</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-177290000</v>
+        <v>-28097000</v>
       </c>
       <c r="AF5" t="n">
-        <v>7160000</v>
+        <v>-2802000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-170130000</v>
+        <v>-30899000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1427000</v>
+        <v>44000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3524000</v>
+        <v>-3803000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-3524000</v>
+        <v>3803000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-99552000</v>
+        <v>-6650000</v>
       </c>
       <c r="AL5" t="n">
-        <v>101839000</v>
+        <v>7314000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2287000</v>
+        <v>664000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-64432000</v>
+        <v>-8510000</v>
       </c>
       <c r="AO5" t="n">
-        <v>225509000</v>
+        <v>51169000</v>
       </c>
       <c r="AP5" t="n">
-        <v>93603000</v>
+        <v>1873000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>132186000</v>
+        <v>49313000</v>
       </c>
       <c r="AR5" t="n">
-        <v>23719000</v>
+        <v>7760000</v>
       </c>
       <c r="AS5" t="n">
-        <v>108467000</v>
+        <v>41553000</v>
       </c>
       <c r="AT5" t="n">
-        <v>161077000</v>
+        <v>42659000</v>
       </c>
       <c r="AU5" t="n">
-        <v>767708000</v>
+        <v>139426000</v>
       </c>
       <c r="AV5" t="n">
-        <v>928785000</v>
+        <v>182085000</v>
       </c>
       <c r="AW5" t="n">
-        <v>928785000</v>
+        <v>182085000</v>
       </c>
     </row>
   </sheetData>
@@ -1574,752 +1574,752 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>7560191876</v>
+        <v>6225126000</v>
       </c>
       <c r="C2" t="n">
-        <v>7560191876</v>
+        <v>6225126000</v>
       </c>
       <c r="D2" t="n">
-        <v>18130000</v>
+        <v>493566000</v>
       </c>
       <c r="E2" t="n">
-        <v>108093000</v>
+        <v>1224564000</v>
       </c>
       <c r="F2" t="n">
-        <v>226083000</v>
+        <v>1124648000</v>
       </c>
       <c r="G2" t="n">
-        <v>254857000</v>
+        <v>1649679000</v>
       </c>
       <c r="H2" t="n">
-        <v>-38467000</v>
+        <v>219536000</v>
       </c>
       <c r="I2" t="n">
-        <v>226083000</v>
+        <v>1124648000</v>
       </c>
       <c r="J2" t="n">
-        <v>79319000</v>
+        <v>703565000</v>
       </c>
       <c r="K2" t="n">
-        <v>226083000</v>
+        <v>1128680000</v>
       </c>
       <c r="L2" t="n">
-        <v>226083000</v>
+        <v>1128680000</v>
       </c>
       <c r="M2" t="n">
-        <v>238905000</v>
+        <v>1104396000</v>
       </c>
       <c r="N2" t="n">
-        <v>12822000</v>
+        <v>-24284000</v>
       </c>
       <c r="O2" t="n">
-        <v>226083000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>1128680000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3732000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>-1670438000</v>
+        <v>-1003063000</v>
       </c>
       <c r="R2" t="n">
-        <v>1662112000</v>
+        <v>1669298000</v>
       </c>
       <c r="S2" t="n">
-        <v>756019000</v>
+        <v>622513000</v>
       </c>
       <c r="T2" t="n">
-        <v>756019000</v>
+        <v>622513000</v>
       </c>
       <c r="U2" t="n">
-        <v>204042000</v>
+        <v>1775655000</v>
       </c>
       <c r="V2" t="n">
-        <v>71880000</v>
+        <v>588092000</v>
       </c>
       <c r="W2" t="n">
-        <v>9197000</v>
+        <v>29380000</v>
       </c>
       <c r="X2" t="n">
-        <v>62683000</v>
+        <v>558712000</v>
       </c>
       <c r="Y2" t="n">
-        <v>62683000</v>
+        <v>558712000</v>
       </c>
       <c r="Z2" t="n">
-        <v>132162000</v>
+        <v>1187563000</v>
       </c>
       <c r="AA2" t="n">
-        <v>45410000</v>
+        <v>665852000</v>
       </c>
       <c r="AB2" t="n">
-        <v>16636000</v>
+        <v>144853000</v>
       </c>
       <c r="AC2" t="n">
-        <v>28774000</v>
+        <v>520999000</v>
       </c>
       <c r="AD2" t="n">
-        <v>72827000</v>
+        <v>218599000</v>
       </c>
       <c r="AE2" t="n">
-        <v>54695000</v>
+        <v>69036000</v>
       </c>
       <c r="AF2" t="n">
-        <v>272000</v>
+        <v>8825000</v>
       </c>
       <c r="AG2" t="n">
-        <v>17860000</v>
+        <v>140738000</v>
       </c>
       <c r="AH2" t="n">
-        <v>442947000</v>
+        <v>2880051000</v>
       </c>
       <c r="AI2" t="n">
-        <v>349252000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+        <v>1472952000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-270000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>4298000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>284605000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>284605000</v>
       </c>
       <c r="AN2" t="n">
-        <v>284840000</v>
+        <v>454913000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>4032000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>4032000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>64412000</v>
+        <v>725104000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-31279000</v>
+        <v>-137871000</v>
       </c>
       <c r="AS2" t="n">
-        <v>95691000</v>
+        <v>862975000</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>23975000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>38915000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>3842000</v>
+        <v>4229000</v>
       </c>
       <c r="AW2" t="n">
-        <v>91849000</v>
+        <v>795856000</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>93695000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>1407099000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA2" t="n">
-        <v>33937000</v>
+        <v>249918000</v>
       </c>
       <c r="BB2" t="n">
-        <v>6551000</v>
+        <v>508934000</v>
       </c>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>6551000</v>
+        <v>473079000</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>35855000</v>
       </c>
       <c r="BF2" t="n">
-        <v>30354000</v>
+        <v>484125000</v>
       </c>
       <c r="BG2" t="n">
-        <v>12209000</v>
+        <v>136689000</v>
       </c>
       <c r="BH2" t="n">
-        <v>-113000</v>
+        <v>-19184000</v>
       </c>
       <c r="BI2" t="n">
-        <v>12322000</v>
+        <v>155873000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10644000</v>
+        <v>27433000</v>
       </c>
       <c r="BK2" t="n">
-        <v>10644000</v>
+        <v>27433000</v>
       </c>
       <c r="BL2" t="n">
-        <v>10644000</v>
+        <v>27433000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>6332312083</v>
+        <v>6313366083</v>
       </c>
       <c r="C3" t="n">
-        <v>6332312083</v>
+        <v>6313366083</v>
       </c>
       <c r="D3" t="n">
-        <v>428657000</v>
+        <v>425164000</v>
       </c>
       <c r="E3" t="n">
-        <v>553357000</v>
+        <v>591050000</v>
       </c>
       <c r="F3" t="n">
-        <v>616406000</v>
+        <v>798137000</v>
       </c>
       <c r="G3" t="n">
-        <v>1061664000</v>
+        <v>1241856000</v>
       </c>
       <c r="H3" t="n">
-        <v>35974000</v>
+        <v>161197000</v>
       </c>
       <c r="I3" t="n">
-        <v>616406000</v>
+        <v>798137000</v>
       </c>
       <c r="J3" t="n">
-        <v>111704000</v>
+        <v>151006000</v>
       </c>
       <c r="K3" t="n">
-        <v>620011000</v>
+        <v>801812000</v>
       </c>
       <c r="L3" t="n">
-        <v>620011000</v>
+        <v>801812000</v>
       </c>
       <c r="M3" t="n">
-        <v>611237000</v>
+        <v>785634000</v>
       </c>
       <c r="N3" t="n">
-        <v>-8774000</v>
+        <v>-16178000</v>
       </c>
       <c r="O3" t="n">
-        <v>620011000</v>
+        <v>801812000</v>
       </c>
       <c r="P3" t="n">
-        <v>101000</v>
+        <v>648000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1374731000</v>
+        <v>-1221414000</v>
       </c>
       <c r="R3" t="n">
-        <v>1662112000</v>
+        <v>1663459000</v>
       </c>
       <c r="S3" t="n">
-        <v>633231000</v>
+        <v>631337000</v>
       </c>
       <c r="T3" t="n">
-        <v>633231000</v>
+        <v>631337000</v>
       </c>
       <c r="U3" t="n">
-        <v>1250995000</v>
+        <v>1159340000</v>
       </c>
       <c r="V3" t="n">
-        <v>103369000</v>
+        <v>136883000</v>
       </c>
       <c r="W3" t="n">
-        <v>24073000</v>
+        <v>24446000</v>
       </c>
       <c r="X3" t="n">
-        <v>79296000</v>
+        <v>112437000</v>
       </c>
       <c r="Y3" t="n">
-        <v>79296000</v>
+        <v>112437000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1147626000</v>
+        <v>1022457000</v>
       </c>
       <c r="AA3" t="n">
-        <v>474061000</v>
+        <v>478613000</v>
       </c>
       <c r="AB3" t="n">
-        <v>32408000</v>
+        <v>38569000</v>
       </c>
       <c r="AC3" t="n">
-        <v>441653000</v>
+        <v>440044000</v>
       </c>
       <c r="AD3" t="n">
-        <v>213652000</v>
+        <v>208885000</v>
       </c>
       <c r="AE3" t="n">
-        <v>60878000</v>
+        <v>46133000</v>
       </c>
       <c r="AF3" t="n">
-        <v>5953000</v>
+        <v>5461000</v>
       </c>
       <c r="AG3" t="n">
-        <v>146821000</v>
+        <v>157291000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1862232000</v>
+        <v>1944974000</v>
       </c>
       <c r="AI3" t="n">
-        <v>678632000</v>
+        <v>761320000</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
       <c r="AL3" t="n">
-        <v>169772000</v>
+        <v>204738000</v>
       </c>
       <c r="AM3" t="n">
-        <v>169772000</v>
+        <v>204738000</v>
       </c>
       <c r="AN3" t="n">
-        <v>403448000</v>
+        <v>412381000</v>
       </c>
       <c r="AO3" t="n">
-        <v>3605000</v>
+        <v>3675000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3605000</v>
+        <v>3675000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>101807000</v>
+        <v>140526000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-139138000</v>
+        <v>-137667000</v>
       </c>
       <c r="AS3" t="n">
-        <v>240945000</v>
+        <v>278193000</v>
       </c>
       <c r="AT3" t="n">
-        <v>21478000</v>
+        <v>21896000</v>
       </c>
       <c r="AU3" t="n">
-        <v>31400000</v>
+        <v>35358000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3101000</v>
+        <v>4088000</v>
       </c>
       <c r="AW3" t="n">
-        <v>216366000</v>
+        <v>216851000</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1183600000</v>
+        <v>1183654000</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>146235000</v>
+        <v>152370000</v>
       </c>
       <c r="BB3" t="n">
-        <v>562170000</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>533331000</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>149351000</v>
+      </c>
       <c r="BD3" t="n">
-        <v>539134000</v>
+        <v>492255000</v>
       </c>
       <c r="BE3" t="n">
-        <v>23036000</v>
+        <v>41076000</v>
       </c>
       <c r="BF3" t="n">
-        <v>335412000</v>
+        <v>337506000</v>
       </c>
       <c r="BG3" t="n">
-        <v>126787000</v>
+        <v>145567000</v>
       </c>
       <c r="BH3" t="n">
-        <v>-26160000</v>
+        <v>-18876000</v>
       </c>
       <c r="BI3" t="n">
-        <v>152947000</v>
+        <v>164443000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12996000</v>
+        <v>14880000</v>
       </c>
       <c r="BK3" t="n">
-        <v>12996000</v>
+        <v>14880000</v>
       </c>
       <c r="BL3" t="n">
-        <v>12996000</v>
+        <v>14880000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>6313366083</v>
+        <v>6332312083</v>
       </c>
       <c r="C4" t="n">
-        <v>6313366083</v>
+        <v>6332312083</v>
       </c>
       <c r="D4" t="n">
-        <v>425164000</v>
+        <v>428657000</v>
       </c>
       <c r="E4" t="n">
-        <v>591050000</v>
+        <v>553357000</v>
       </c>
       <c r="F4" t="n">
-        <v>798137000</v>
+        <v>616406000</v>
       </c>
       <c r="G4" t="n">
-        <v>1241856000</v>
+        <v>1061664000</v>
       </c>
       <c r="H4" t="n">
-        <v>161197000</v>
+        <v>35974000</v>
       </c>
       <c r="I4" t="n">
-        <v>798137000</v>
+        <v>616406000</v>
       </c>
       <c r="J4" t="n">
-        <v>151006000</v>
+        <v>111704000</v>
       </c>
       <c r="K4" t="n">
-        <v>801812000</v>
+        <v>620011000</v>
       </c>
       <c r="L4" t="n">
-        <v>801812000</v>
+        <v>620011000</v>
       </c>
       <c r="M4" t="n">
-        <v>785634000</v>
+        <v>611237000</v>
       </c>
       <c r="N4" t="n">
-        <v>-16178000</v>
+        <v>-8774000</v>
       </c>
       <c r="O4" t="n">
-        <v>801812000</v>
+        <v>620011000</v>
       </c>
       <c r="P4" t="n">
-        <v>648000</v>
+        <v>101000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1221414000</v>
+        <v>-1374731000</v>
       </c>
       <c r="R4" t="n">
-        <v>1663459000</v>
+        <v>1662112000</v>
       </c>
       <c r="S4" t="n">
-        <v>631337000</v>
+        <v>633231000</v>
       </c>
       <c r="T4" t="n">
-        <v>631337000</v>
+        <v>633231000</v>
       </c>
       <c r="U4" t="n">
-        <v>1159340000</v>
+        <v>1250995000</v>
       </c>
       <c r="V4" t="n">
-        <v>136883000</v>
+        <v>103369000</v>
       </c>
       <c r="W4" t="n">
-        <v>24446000</v>
+        <v>24073000</v>
       </c>
       <c r="X4" t="n">
-        <v>112437000</v>
+        <v>79296000</v>
       </c>
       <c r="Y4" t="n">
-        <v>112437000</v>
+        <v>79296000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1022457000</v>
+        <v>1147626000</v>
       </c>
       <c r="AA4" t="n">
-        <v>478613000</v>
+        <v>474061000</v>
       </c>
       <c r="AB4" t="n">
-        <v>38569000</v>
+        <v>32408000</v>
       </c>
       <c r="AC4" t="n">
-        <v>440044000</v>
+        <v>441653000</v>
       </c>
       <c r="AD4" t="n">
-        <v>208885000</v>
+        <v>213652000</v>
       </c>
       <c r="AE4" t="n">
-        <v>46133000</v>
+        <v>60878000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5461000</v>
+        <v>5953000</v>
       </c>
       <c r="AG4" t="n">
-        <v>157291000</v>
+        <v>146821000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1944974000</v>
+        <v>1862232000</v>
       </c>
       <c r="AI4" t="n">
-        <v>761320000</v>
+        <v>678632000</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>204738000</v>
+        <v>169772000</v>
       </c>
       <c r="AM4" t="n">
-        <v>204738000</v>
+        <v>169772000</v>
       </c>
       <c r="AN4" t="n">
-        <v>412381000</v>
+        <v>403448000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3675000</v>
+        <v>3605000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3675000</v>
+        <v>3605000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>140526000</v>
+        <v>101807000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-137667000</v>
+        <v>-139138000</v>
       </c>
       <c r="AS4" t="n">
-        <v>278193000</v>
+        <v>240945000</v>
       </c>
       <c r="AT4" t="n">
-        <v>21896000</v>
+        <v>21478000</v>
       </c>
       <c r="AU4" t="n">
-        <v>35358000</v>
+        <v>31400000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4088000</v>
+        <v>3101000</v>
       </c>
       <c r="AW4" t="n">
-        <v>216851000</v>
+        <v>216366000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1183654000</v>
+        <v>1183600000</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>152370000</v>
+        <v>146235000</v>
       </c>
       <c r="BB4" t="n">
-        <v>533331000</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>149351000</v>
-      </c>
+        <v>562170000</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>492255000</v>
+        <v>539134000</v>
       </c>
       <c r="BE4" t="n">
-        <v>41076000</v>
+        <v>23036000</v>
       </c>
       <c r="BF4" t="n">
-        <v>337506000</v>
+        <v>335412000</v>
       </c>
       <c r="BG4" t="n">
-        <v>145567000</v>
+        <v>126787000</v>
       </c>
       <c r="BH4" t="n">
-        <v>-18876000</v>
+        <v>-26160000</v>
       </c>
       <c r="BI4" t="n">
-        <v>164443000</v>
+        <v>152947000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>14880000</v>
+        <v>12996000</v>
       </c>
       <c r="BK4" t="n">
-        <v>14880000</v>
+        <v>12996000</v>
       </c>
       <c r="BL4" t="n">
-        <v>14880000</v>
+        <v>12996000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>6225126000</v>
+        <v>7560191876</v>
       </c>
       <c r="C5" t="n">
-        <v>6225126000</v>
+        <v>7560191876</v>
       </c>
       <c r="D5" t="n">
-        <v>493566000</v>
+        <v>18130000</v>
       </c>
       <c r="E5" t="n">
-        <v>1224564000</v>
+        <v>108093000</v>
       </c>
       <c r="F5" t="n">
-        <v>1124648000</v>
+        <v>226083000</v>
       </c>
       <c r="G5" t="n">
-        <v>1649679000</v>
+        <v>254857000</v>
       </c>
       <c r="H5" t="n">
-        <v>219536000</v>
+        <v>-38467000</v>
       </c>
       <c r="I5" t="n">
-        <v>1124648000</v>
+        <v>226083000</v>
       </c>
       <c r="J5" t="n">
-        <v>703565000</v>
+        <v>79319000</v>
       </c>
       <c r="K5" t="n">
-        <v>1128680000</v>
+        <v>226083000</v>
       </c>
       <c r="L5" t="n">
-        <v>1128680000</v>
+        <v>226083000</v>
       </c>
       <c r="M5" t="n">
-        <v>1104396000</v>
+        <v>238905000</v>
       </c>
       <c r="N5" t="n">
-        <v>-24284000</v>
+        <v>12822000</v>
       </c>
       <c r="O5" t="n">
-        <v>1128680000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3732000</v>
-      </c>
+        <v>226083000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-1003063000</v>
+        <v>-1670438000</v>
       </c>
       <c r="R5" t="n">
-        <v>1669298000</v>
+        <v>1662112000</v>
       </c>
       <c r="S5" t="n">
-        <v>622513000</v>
+        <v>756019000</v>
       </c>
       <c r="T5" t="n">
-        <v>622513000</v>
+        <v>756019000</v>
       </c>
       <c r="U5" t="n">
-        <v>1775655000</v>
+        <v>204042000</v>
       </c>
       <c r="V5" t="n">
-        <v>588092000</v>
+        <v>71880000</v>
       </c>
       <c r="W5" t="n">
-        <v>29380000</v>
+        <v>9197000</v>
       </c>
       <c r="X5" t="n">
-        <v>558712000</v>
+        <v>62683000</v>
       </c>
       <c r="Y5" t="n">
-        <v>558712000</v>
+        <v>62683000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1187563000</v>
+        <v>132162000</v>
       </c>
       <c r="AA5" t="n">
-        <v>665852000</v>
+        <v>45410000</v>
       </c>
       <c r="AB5" t="n">
-        <v>144853000</v>
+        <v>16636000</v>
       </c>
       <c r="AC5" t="n">
-        <v>520999000</v>
+        <v>28774000</v>
       </c>
       <c r="AD5" t="n">
-        <v>218599000</v>
+        <v>72827000</v>
       </c>
       <c r="AE5" t="n">
-        <v>69036000</v>
+        <v>54695000</v>
       </c>
       <c r="AF5" t="n">
-        <v>8825000</v>
+        <v>272000</v>
       </c>
       <c r="AG5" t="n">
-        <v>140738000</v>
+        <v>17860000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2880051000</v>
+        <v>442947000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1472952000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-270000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>4298000</v>
-      </c>
+        <v>349252000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>284605000</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>284605000</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>454913000</v>
+        <v>284840000</v>
       </c>
       <c r="AO5" t="n">
-        <v>4032000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>4032000</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>725104000</v>
+        <v>64412000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-137871000</v>
+        <v>-31279000</v>
       </c>
       <c r="AS5" t="n">
-        <v>862975000</v>
+        <v>95691000</v>
       </c>
       <c r="AT5" t="n">
-        <v>23975000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>38915000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>4229000</v>
+        <v>3842000</v>
       </c>
       <c r="AW5" t="n">
-        <v>795856000</v>
+        <v>91849000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1407099000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
+        <v>93695000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>249918000</v>
+        <v>33937000</v>
       </c>
       <c r="BB5" t="n">
-        <v>508934000</v>
+        <v>6551000</v>
       </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>473079000</v>
+        <v>6551000</v>
       </c>
       <c r="BE5" t="n">
-        <v>35855000</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>484125000</v>
+        <v>30354000</v>
       </c>
       <c r="BG5" t="n">
-        <v>136689000</v>
+        <v>12209000</v>
       </c>
       <c r="BH5" t="n">
-        <v>-19184000</v>
+        <v>-113000</v>
       </c>
       <c r="BI5" t="n">
-        <v>155873000</v>
+        <v>12322000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>27433000</v>
+        <v>10644000</v>
       </c>
       <c r="BK5" t="n">
-        <v>27433000</v>
+        <v>10644000</v>
       </c>
       <c r="BL5" t="n">
-        <v>27433000</v>
+        <v>10644000</v>
       </c>
     </row>
   </sheetData>
@@ -2595,562 +2595,562 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-137451000</v>
+        <v>168969000</v>
       </c>
       <c r="C2" t="n">
-        <v>-13106000</v>
+        <v>-98855000</v>
       </c>
       <c r="D2" t="n">
-        <v>25233000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>122788000</v>
-      </c>
+        <v>110287000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-8723000</v>
+        <v>-5390000</v>
       </c>
       <c r="G2" t="n">
-        <v>10644000</v>
+        <v>27433000</v>
       </c>
       <c r="H2" t="n">
-        <v>12996000</v>
+        <v>26115000</v>
       </c>
       <c r="I2" t="n">
-        <v>482000</v>
+        <v>-7642000</v>
       </c>
       <c r="J2" t="n">
-        <v>-2834000</v>
+        <v>8960000</v>
       </c>
       <c r="K2" t="n">
-        <v>134487000</v>
+        <v>-160064000</v>
       </c>
       <c r="L2" t="n">
-        <v>37493000</v>
+        <v>32360000</v>
       </c>
       <c r="M2" t="n">
-        <v>-108000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>122788000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>122788000</v>
-      </c>
+        <v>-13021000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>12127000</v>
+        <v>11432000</v>
       </c>
       <c r="Q2" t="n">
-        <v>25233000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>11432000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-98855000</v>
+      </c>
       <c r="S2" t="n">
-        <v>25233000</v>
+        <v>110287000</v>
       </c>
       <c r="T2" t="n">
-        <v>-13106000</v>
+        <v>11432000</v>
       </c>
       <c r="U2" t="n">
-        <v>-13106000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>-98855000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>110287000</v>
+      </c>
       <c r="W2" t="n">
-        <v>-8593000</v>
+        <v>-5335000</v>
       </c>
       <c r="X2" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+        <v>55000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-8614000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>109000</v>
-      </c>
+        <v>-5390000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>-8723000</v>
+        <v>-5390000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-128728000</v>
+        <v>174359000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-3524000</v>
+        <v>-1063000</v>
       </c>
       <c r="AK2" t="n">
-        <v>116215000</v>
+        <v>-21100000</v>
       </c>
       <c r="AL2" t="n">
-        <v>7162000</v>
+        <v>19690000</v>
       </c>
       <c r="AM2" t="n">
-        <v>123730000</v>
+        <v>5713000</v>
       </c>
       <c r="AN2" t="n">
-        <v>18244000</v>
+        <v>142950000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1724000</v>
+        <v>-139653000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-34645000</v>
+        <v>-49800000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6650000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>99552000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3732000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>1873000</v>
+        <v>58937000</v>
       </c>
       <c r="AT2" t="n">
-        <v>36819000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>162069000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9484000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>36819000</v>
+        <v>152585000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1750000</v>
+        <v>-9866000</v>
       </c>
       <c r="AX2" t="n">
-        <v>3803000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>-3401000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>-302544000</v>
+        <v>-170130000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>50947000</v>
+        <v>258372000</v>
       </c>
       <c r="C3" t="n">
-        <v>-23753000</v>
+        <v>-92693000</v>
       </c>
       <c r="D3" t="n">
-        <v>27857000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+        <v>40748000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-6863000</v>
+        <v>-293000</v>
       </c>
       <c r="G3" t="n">
-        <v>12996000</v>
+        <v>14880000</v>
       </c>
       <c r="H3" t="n">
-        <v>14880000</v>
+        <v>27433000</v>
       </c>
       <c r="I3" t="n">
-        <v>-5261000</v>
+        <v>-3270000</v>
       </c>
       <c r="J3" t="n">
-        <v>3377000</v>
+        <v>-9283000</v>
       </c>
       <c r="K3" t="n">
-        <v>-47622000</v>
+        <v>-253604000</v>
       </c>
       <c r="L3" t="n">
-        <v>3209000</v>
+        <v>-17391000</v>
       </c>
       <c r="M3" t="n">
-        <v>-7509000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>-16364000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>4104000</v>
+        <v>-51945000</v>
       </c>
       <c r="Q3" t="n">
-        <v>27857000</v>
+        <v>-51945000</v>
       </c>
       <c r="R3" t="n">
-        <v>-23753000</v>
+        <v>-92693000</v>
       </c>
       <c r="S3" t="n">
-        <v>27857000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-23753000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-23753000</v>
-      </c>
+        <v>40748000</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-6811000</v>
+        <v>-14344000</v>
       </c>
       <c r="X3" t="n">
-        <v>52000</v>
+        <v>34000</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-14085000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-14085000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-6863000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
+        <v>-293000</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-6863000</v>
+        <v>-293000</v>
       </c>
       <c r="AI3" t="n">
-        <v>57810000</v>
+        <v>258665000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-56000</v>
+        <v>-13000</v>
       </c>
       <c r="AK3" t="n">
-        <v>33507000</v>
+        <v>70765000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-19878000</v>
+        <v>-34202000</v>
       </c>
       <c r="AM3" t="n">
-        <v>61281000</v>
+        <v>57439000</v>
       </c>
       <c r="AN3" t="n">
-        <v>18279000</v>
+        <v>45064000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-39323000</v>
+        <v>-53490000</v>
       </c>
       <c r="AP3" t="n">
-        <v>13148000</v>
+        <v>55954000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>99941000</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>146375000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
       <c r="AS3" t="n">
-        <v>414000</v>
+        <v>40351000</v>
       </c>
       <c r="AT3" t="n">
-        <v>45277000</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>164923000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
       <c r="AV3" t="n">
-        <v>45277000</v>
+        <v>164923000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1121000</v>
+        <v>2325000</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-627000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-144862000</v>
+        <v>-224271000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>258372000</v>
+        <v>50947000</v>
       </c>
       <c r="C4" t="n">
-        <v>-92693000</v>
+        <v>-23753000</v>
       </c>
       <c r="D4" t="n">
-        <v>40748000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>27857000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
-        <v>-293000</v>
+        <v>-6863000</v>
       </c>
       <c r="G4" t="n">
+        <v>12996000</v>
+      </c>
+      <c r="H4" t="n">
         <v>14880000</v>
       </c>
-      <c r="H4" t="n">
-        <v>27433000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-3270000</v>
+        <v>-5261000</v>
       </c>
       <c r="J4" t="n">
-        <v>-9283000</v>
+        <v>3377000</v>
       </c>
       <c r="K4" t="n">
-        <v>-253604000</v>
+        <v>-47622000</v>
       </c>
       <c r="L4" t="n">
-        <v>-17391000</v>
+        <v>3209000</v>
       </c>
       <c r="M4" t="n">
-        <v>-16364000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>-7509000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>-51945000</v>
+        <v>4104000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-51945000</v>
+        <v>27857000</v>
       </c>
       <c r="R4" t="n">
-        <v>-92693000</v>
+        <v>-23753000</v>
       </c>
       <c r="S4" t="n">
-        <v>40748000</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>27857000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-23753000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-23753000</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-14344000</v>
+        <v>-6811000</v>
       </c>
       <c r="X4" t="n">
-        <v>34000</v>
+        <v>52000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>-14085000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-14085000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-293000</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>-6863000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH4" t="n">
-        <v>-293000</v>
+        <v>-6863000</v>
       </c>
       <c r="AI4" t="n">
-        <v>258665000</v>
+        <v>57810000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-13000</v>
+        <v>-56000</v>
       </c>
       <c r="AK4" t="n">
-        <v>70765000</v>
+        <v>33507000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-34202000</v>
+        <v>-19878000</v>
       </c>
       <c r="AM4" t="n">
-        <v>57439000</v>
+        <v>61281000</v>
       </c>
       <c r="AN4" t="n">
-        <v>45064000</v>
+        <v>18279000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-53490000</v>
+        <v>-39323000</v>
       </c>
       <c r="AP4" t="n">
-        <v>55954000</v>
+        <v>13148000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>146375000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
+        <v>99941000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>40351000</v>
+        <v>414000</v>
       </c>
       <c r="AT4" t="n">
-        <v>164923000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
+        <v>45277000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>164923000</v>
+        <v>45277000</v>
       </c>
       <c r="AW4" t="n">
-        <v>2325000</v>
+        <v>1121000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>-627000</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-224271000</v>
+        <v>-144862000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>168969000</v>
+        <v>-137451000</v>
       </c>
       <c r="C5" t="n">
-        <v>-98855000</v>
+        <v>-13106000</v>
       </c>
       <c r="D5" t="n">
-        <v>110287000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>25233000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>122788000</v>
+      </c>
       <c r="F5" t="n">
-        <v>-5390000</v>
+        <v>-8723000</v>
       </c>
       <c r="G5" t="n">
-        <v>27433000</v>
+        <v>10644000</v>
       </c>
       <c r="H5" t="n">
-        <v>26115000</v>
+        <v>12996000</v>
       </c>
       <c r="I5" t="n">
-        <v>-7642000</v>
+        <v>482000</v>
       </c>
       <c r="J5" t="n">
-        <v>8960000</v>
+        <v>-2834000</v>
       </c>
       <c r="K5" t="n">
-        <v>-160064000</v>
+        <v>134487000</v>
       </c>
       <c r="L5" t="n">
-        <v>32360000</v>
+        <v>37493000</v>
       </c>
       <c r="M5" t="n">
-        <v>-13021000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>-108000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>122788000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>122788000</v>
+      </c>
       <c r="P5" t="n">
-        <v>11432000</v>
+        <v>12127000</v>
       </c>
       <c r="Q5" t="n">
-        <v>11432000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-98855000</v>
-      </c>
+        <v>25233000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>110287000</v>
+        <v>25233000</v>
       </c>
       <c r="T5" t="n">
-        <v>11432000</v>
+        <v>-13106000</v>
       </c>
       <c r="U5" t="n">
-        <v>-98855000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>110287000</v>
-      </c>
+        <v>-13106000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-5335000</v>
+        <v>-8593000</v>
       </c>
       <c r="X5" t="n">
-        <v>55000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
+        <v>21000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-5390000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>-8614000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>109000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>-5390000</v>
+        <v>-8723000</v>
       </c>
       <c r="AI5" t="n">
-        <v>174359000</v>
+        <v>-128728000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1063000</v>
+        <v>-3524000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-21100000</v>
+        <v>116215000</v>
       </c>
       <c r="AL5" t="n">
-        <v>19690000</v>
+        <v>7162000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5713000</v>
+        <v>123730000</v>
       </c>
       <c r="AN5" t="n">
-        <v>142950000</v>
+        <v>18244000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-139653000</v>
+        <v>1724000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-49800000</v>
+        <v>-34645000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>99552000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3732000</v>
-      </c>
+        <v>6650000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>58937000</v>
+        <v>1873000</v>
       </c>
       <c r="AT5" t="n">
-        <v>162069000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9484000</v>
-      </c>
+        <v>36819000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>152585000</v>
+        <v>36819000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-9866000</v>
+        <v>1750000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-3401000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
+        <v>3803000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>-170130000</v>
+        <v>-302544000</v>
       </c>
     </row>
   </sheetData>
@@ -3690,187 +3690,187 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.139</v>
+        <v>-0.121</v>
       </c>
       <c r="AF2" t="n">
         <v>34368000</v>
@@ -4012,7 +4012,7 @@
         <v>34368000</v>
       </c>
       <c r="AH2" t="n">
-        <v>3359666</v>
+        <v>2804677</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -4054,10 +4054,10 @@
         <v>1.4904206</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.04638</v>
+        <v>0.045</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.07589</v>
+        <v>0.072605</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4130,10 +4130,10 @@
         <v>-17.873</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.59821427</v>
+        <v>-0.6017699</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.01375</v>
@@ -4248,137 +4248,137 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>2804677</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.0020000003</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.046511635</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>0.043 - 0.166</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.12099999</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.72891563</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-60.176994</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1743432759</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1743432759</v>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.027604997</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.38020796</v>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>979695000000</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.0009999983000000001</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>0.043 - 0.051</t>
+        </is>
+      </c>
+      <c r="DV2" t="n">
+        <v>1774943997</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>finmb_9736054</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>China Beidahuang Industry Group Holdings Limited</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>CH BEIDAHUANG</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="n">
         <v>-2.1739094</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="EJ2" t="n">
         <v>0.045</v>
       </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>finmb_9736054</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>1774943997</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>3359666</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.0020000003</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.046511635</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0.043 - 0.166</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.12099999</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.72891563</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-59.821426</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1743432759</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1743432759</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.0013799965</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.02975413</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.030889995</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.40703645</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>979695000000</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.0009999983000000001</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>0.043 - 0.051</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>CH BEIDAHUANG</t>
-        </is>
-      </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>China Beidahuang Industry Group Holdings Limited</t>
+          <t>PREPRE</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr"/>
